--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_hdensity_tests.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_hdensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80.31***</t>
+          <t>82.26***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.72***</t>
+          <t>14.66***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6525.21***</t>
+          <t>6981.62***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.88***</t>
+          <t>77.25***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.62***</t>
+          <t>76.28***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.31***</t>
+          <t>82.26***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.06***</t>
+          <t>4.92***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6465.62***</t>
+          <t>6790.95***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.06***</t>
+          <t>19.15***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.62***</t>
+          <t>76.28***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>80.31***</t>
+          <t>82.26***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.26***</t>
+          <t>4.08***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6459.74***</t>
+          <t>6783.36***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.19***</t>
+          <t>13.70***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.62***</t>
+          <t>76.28***</t>
         </is>
       </c>
     </row>
